--- a/VerveStacks_POL_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A11BB3-5170-4F63-A6AE-D92E3EB65FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E368DF-A1FD-41F2-81A1-2A5A3FFB4CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_POL_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E368DF-A1FD-41F2-81A1-2A5A3FFB4CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C9278A0-B65B-4FD0-A0C4-9DB0D28B341D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Veda" sheetId="1" r:id="rId1"/>
@@ -1249,19 +1249,19 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>241.69</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>339.03</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>410.28</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>494.2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>635.42999999999995</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6041,13 +6041,13 @@
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.45">
       <c r="D3" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K3" s="10">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="L3" s="10" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N3" s="10" t="s">
         <v>115</v>
@@ -6058,10 +6058,10 @@
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.45">
       <c r="K4" s="10">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N4" s="10" t="s">
         <v>82</v>
@@ -6077,7 +6077,7 @@
       </c>
       <c r="E5" s="1">
         <f>VLOOKUP(D3,$C$9:$E$999,3,FALSE)</f>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="K5" s="10">
         <v>100</v>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="B11" t="str">
         <f t="shared" si="0"/>
-        <v>base·$200</v>
+        <v>base·$300</v>
       </c>
       <c r="C11">
         <f>C10+1</f>
@@ -6220,7 +6220,7 @@
         <v>115</v>
       </c>
       <c r="E11" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="S11" s="22">
         <f>SUMIFS(iea_data!I3:I9999,iea_data!$B$3:$B$9999,Veda!$S$10)+T28-T29</f>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="B12" t="str">
         <f t="shared" si="0"/>
-        <v>base·$300</v>
+        <v>base·$600</v>
       </c>
       <c r="C12">
         <f>C11+1</f>
@@ -6268,7 +6268,7 @@
         <v>115</v>
       </c>
       <c r="E12" s="15">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="S12" s="22">
         <f>SUMIFS(iea_data!J3:J9999,iea_data!$B$3:$B$9999,Veda!$S$10)</f>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="B15" t="str">
         <f t="shared" si="0"/>
-        <v>high·$200</v>
+        <v>high·$300</v>
       </c>
       <c r="C15">
         <f t="shared" si="2"/>
@@ -6453,7 +6453,7 @@
       </c>
       <c r="E15" s="15">
         <f t="shared" si="3"/>
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G15" t="s">
         <v>114</v>
@@ -6507,7 +6507,7 @@
       </c>
       <c r="B16" t="str">
         <f t="shared" si="0"/>
-        <v>high·$300</v>
+        <v>high·$600</v>
       </c>
       <c r="C16">
         <f t="shared" si="2"/>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="E16" s="15">
         <f t="shared" si="3"/>
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="S16" s="5" t="s">
         <v>12</v>
@@ -7011,7 +7011,7 @@
       </c>
       <c r="H24" s="3" t="str">
         <f>VLOOKUP(E5,$K$3:$L$6,2,FALSE)</f>
-        <v>C7</v>
+        <v>C1</v>
       </c>
       <c r="I24" s="8">
         <v>0</v>
@@ -7021,23 +7021,23 @@
       </c>
       <c r="K24" s="8">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$24,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$G24)</f>
-        <v>0</v>
+        <v>241.69</v>
       </c>
       <c r="L24" s="8">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$24,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$G24)</f>
-        <v>0</v>
+        <v>339.03</v>
       </c>
       <c r="M24" s="8">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$24,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$G24)</f>
-        <v>0</v>
+        <v>410.28</v>
       </c>
       <c r="N24" s="8">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$24,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$G24)</f>
-        <v>0</v>
+        <v>494.2</v>
       </c>
       <c r="O24" s="8">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$H$24,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$G24)</f>
-        <v>0</v>
+        <v>635.42999999999995</v>
       </c>
       <c r="S24" s="26" t="s">
         <v>27</v>
@@ -7048,23 +7048,23 @@
       </c>
       <c r="V24" s="28">
         <f>K24/1000</f>
-        <v>0</v>
+        <v>0.24168999999999999</v>
       </c>
       <c r="W24" s="28">
         <f>L24/1000</f>
-        <v>0</v>
+        <v>0.33903</v>
       </c>
       <c r="X24" s="28">
         <f>M24/1000</f>
-        <v>0</v>
+        <v>0.41027999999999998</v>
       </c>
       <c r="Y24" s="28">
         <f>N24/1000</f>
-        <v>0</v>
+        <v>0.49419999999999997</v>
       </c>
       <c r="Z24" s="28">
         <f>O24/1000</f>
-        <v>0</v>
+        <v>0.63542999999999994</v>
       </c>
       <c r="AA24" s="29" t="s">
         <v>28</v>
